--- a/docs/downloads/09/t10_sources_endettement_alaotra_analamiranga.xlsx
+++ b/docs/downloads/09/t10_sources_endettement_alaotra_analamiranga.xlsx
@@ -387,12 +387,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -476,12 +458,6 @@
         <is>
           <t>Autres</t>
         </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1.6</v>
       </c>
     </row>
     <row r="8">
